--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:49:03+00:00</t>
+    <t>2024-01-29T09:55:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T09:55:21+00:00</t>
+    <t>2024-01-29T12:33:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:33:53+00:00</t>
+    <t>2024-01-29T12:36:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
+++ b/ig/nr-add-vs-cs-to-id/StructureDefinition-fr-core-organization-analysis-section.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-29T12:36:14+00:00</t>
+    <t>2024-01-29T12:40:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
